--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/34.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/34.xlsx
@@ -426,13 +426,13 @@
         <v>-7.452891558959399</v>
       </c>
       <c r="E2">
-        <v>-11.510998083915</v>
+        <v>-10.59102953230875</v>
       </c>
       <c r="F2">
-        <v>-1.985799761771609</v>
+        <v>-1.309393045546061</v>
       </c>
       <c r="G2">
-        <v>-7.691753161306673</v>
+        <v>-7.211251076141589</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.652137832453845</v>
       </c>
       <c r="E3">
-        <v>-11.80723273960076</v>
+        <v>-12.15207150681085</v>
       </c>
       <c r="F3">
-        <v>-1.883868324489727</v>
+        <v>-1.127119910601461</v>
       </c>
       <c r="G3">
-        <v>-7.64939915341736</v>
+        <v>-6.824004588917483</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.810618275597592</v>
       </c>
       <c r="E4">
-        <v>-12.24010504151996</v>
+        <v>-11.28507704414633</v>
       </c>
       <c r="F4">
-        <v>-1.780876576932261</v>
+        <v>-0.5765231504108936</v>
       </c>
       <c r="G4">
-        <v>-7.007766121132625</v>
+        <v>-6.628617688717228</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.848732077075487</v>
       </c>
       <c r="E5">
-        <v>-12.46405166662129</v>
+        <v>-11.80596476687862</v>
       </c>
       <c r="F5">
-        <v>-1.943136355425226</v>
+        <v>-0.8450169064758807</v>
       </c>
       <c r="G5">
-        <v>-7.041346142571982</v>
+        <v>-5.41258057267922</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.736221271442959</v>
       </c>
       <c r="E6">
-        <v>-12.64819300519519</v>
+        <v>-11.28324754064723</v>
       </c>
       <c r="F6">
-        <v>-1.776027314156273</v>
+        <v>-0.7971066210001656</v>
       </c>
       <c r="G6">
-        <v>-7.411405591267717</v>
+        <v>-6.9640700936255</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.441069267300227</v>
       </c>
       <c r="E7">
-        <v>-13.38655616367183</v>
+        <v>-12.49537512133234</v>
       </c>
       <c r="F7">
-        <v>-1.863769646195602</v>
+        <v>-0.2656882229192128</v>
       </c>
       <c r="G7">
-        <v>-6.654011062365771</v>
+        <v>-6.882295489921018</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.966628515516074</v>
       </c>
       <c r="E8">
-        <v>-13.13500396101975</v>
+        <v>-14.65992229836267</v>
       </c>
       <c r="F8">
-        <v>-1.645264549419954</v>
+        <v>-0.3214332072906055</v>
       </c>
       <c r="G8">
-        <v>-6.753861915641234</v>
+        <v>-6.092469367125521</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.325263798902325</v>
       </c>
       <c r="E9">
-        <v>-14.51499754469519</v>
+        <v>-13.62606715393752</v>
       </c>
       <c r="F9">
-        <v>-1.446741331134636</v>
+        <v>-0.2917155267151733</v>
       </c>
       <c r="G9">
-        <v>-6.366792614381337</v>
+        <v>-5.443289525254063</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.559432046383005</v>
       </c>
       <c r="E10">
-        <v>-14.76153672662078</v>
+        <v>-14.59313636369754</v>
       </c>
       <c r="F10">
-        <v>-1.334591153571819</v>
+        <v>-0.2250369209942298</v>
       </c>
       <c r="G10">
-        <v>-6.601301519234851</v>
+        <v>-5.992280548029436</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.712723113086093</v>
       </c>
       <c r="E11">
-        <v>-15.35198633858489</v>
+        <v>-15.74683304426168</v>
       </c>
       <c r="F11">
-        <v>-1.379249268624143</v>
+        <v>-0.1374975389685865</v>
       </c>
       <c r="G11">
-        <v>-5.957437256289693</v>
+        <v>-5.103873404701982</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.847605156645471</v>
       </c>
       <c r="E12">
-        <v>-15.99425075014476</v>
+        <v>-14.36436691377805</v>
       </c>
       <c r="F12">
-        <v>-0.9684734707195077</v>
+        <v>-0.5502307690460374</v>
       </c>
       <c r="G12">
-        <v>-6.307195787197143</v>
+        <v>-5.224474703119373</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.013637257303728</v>
       </c>
       <c r="E13">
-        <v>-16.91568652732949</v>
+        <v>-15.60608354362928</v>
       </c>
       <c r="F13">
-        <v>-0.7599187231862874</v>
+        <v>-0.4053228025395142</v>
       </c>
       <c r="G13">
-        <v>-5.882097128063283</v>
+        <v>-4.949590366976892</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.265455778645217</v>
       </c>
       <c r="E14">
-        <v>-18.51107697717978</v>
+        <v>-16.48956165168172</v>
       </c>
       <c r="F14">
-        <v>-0.7165437492408997</v>
+        <v>0.1852020948333917</v>
       </c>
       <c r="G14">
-        <v>-5.834768788289852</v>
+        <v>-5.367985490464807</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.632681578851667</v>
       </c>
       <c r="E15">
-        <v>-19.22781667226979</v>
+        <v>-17.93777669628271</v>
       </c>
       <c r="F15">
-        <v>-0.6431934724578091</v>
+        <v>1.145929354721813</v>
       </c>
       <c r="G15">
-        <v>-6.205838853225896</v>
+        <v>-4.259106508115143</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.136389363708885</v>
       </c>
       <c r="E16">
-        <v>-19.23988958397424</v>
+        <v>-18.65987810459782</v>
       </c>
       <c r="F16">
-        <v>-0.5574168562653231</v>
+        <v>1.141862070774068</v>
       </c>
       <c r="G16">
-        <v>-4.865203910911092</v>
+        <v>-3.852960184708636</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.7724409603823259</v>
       </c>
       <c r="E17">
-        <v>-20.42168544575598</v>
+        <v>-19.42755860380012</v>
       </c>
       <c r="F17">
-        <v>-0.03722780669672034</v>
+        <v>1.735430389984859</v>
       </c>
       <c r="G17">
-        <v>-5.070893846808004</v>
+        <v>-3.363877705165604</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.5275761129748849</v>
       </c>
       <c r="E18">
-        <v>-20.00670967311509</v>
+        <v>-20.00162419680447</v>
       </c>
       <c r="F18">
-        <v>0.5404043804190142</v>
+        <v>1.859793188167149</v>
       </c>
       <c r="G18">
-        <v>-4.367731347840561</v>
+        <v>-3.703044452879166</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3752757292147319</v>
       </c>
       <c r="E19">
-        <v>-21.22150905346472</v>
+        <v>-20.81393733582637</v>
       </c>
       <c r="F19">
-        <v>0.4376478892039439</v>
+        <v>1.626402329163194</v>
       </c>
       <c r="G19">
-        <v>-5.057850991109211</v>
+        <v>-2.984361775935549</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.287411667955926</v>
       </c>
       <c r="E20">
-        <v>-21.92242626037194</v>
+        <v>-19.28732082073058</v>
       </c>
       <c r="F20">
-        <v>0.7463978159427784</v>
+        <v>1.830705895185247</v>
       </c>
       <c r="G20">
-        <v>-4.775610156230455</v>
+        <v>-2.52220828173088</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.2362962025423297</v>
       </c>
       <c r="E21">
-        <v>-21.24064638462114</v>
+        <v>-22.43231431973959</v>
       </c>
       <c r="F21">
-        <v>1.215611620645308</v>
+        <v>1.532339553840504</v>
       </c>
       <c r="G21">
-        <v>-3.515119050505089</v>
+        <v>-2.813065604424738</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.2000993307458732</v>
       </c>
       <c r="E22">
-        <v>-22.30631405895017</v>
+        <v>-22.05940354215595</v>
       </c>
       <c r="F22">
-        <v>0.9217118363364601</v>
+        <v>1.746956294027412</v>
       </c>
       <c r="G22">
-        <v>-3.882425554312449</v>
+        <v>-3.318711690399847</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.1657822683579971</v>
       </c>
       <c r="E23">
-        <v>-22.61600733938673</v>
+        <v>-23.01959399989833</v>
       </c>
       <c r="F23">
-        <v>1.205982677955167</v>
+        <v>2.059830662064785</v>
       </c>
       <c r="G23">
-        <v>-4.860820198907675</v>
+        <v>-3.058481289741846</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.1268619513559777</v>
       </c>
       <c r="E24">
-        <v>-23.08625313729124</v>
+        <v>-22.42396381366945</v>
       </c>
       <c r="F24">
-        <v>1.278741500412658</v>
+        <v>2.420725488442446</v>
       </c>
       <c r="G24">
-        <v>-4.0039685633174</v>
+        <v>-2.676448663575698</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.08527746454588649</v>
       </c>
       <c r="E25">
-        <v>-23.17556823014452</v>
+        <v>-23.8389126882101</v>
       </c>
       <c r="F25">
-        <v>1.523557202636024</v>
+        <v>1.700526301100499</v>
       </c>
       <c r="G25">
-        <v>-4.435206387988981</v>
+        <v>-1.429121818746824</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.04590840734095061</v>
       </c>
       <c r="E26">
-        <v>-22.15623590186197</v>
+        <v>-23.76134898540672</v>
       </c>
       <c r="F26">
-        <v>1.275633465917354</v>
+        <v>2.263130246794645</v>
       </c>
       <c r="G26">
-        <v>-4.058105437826678</v>
+        <v>-3.792447896709356</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.01707511007708102</v>
       </c>
       <c r="E27">
-        <v>-23.4285967153231</v>
+        <v>-24.29522890006701</v>
       </c>
       <c r="F27">
-        <v>1.333095655914751</v>
+        <v>2.062322391212406</v>
       </c>
       <c r="G27">
-        <v>-4.329236056505155</v>
+        <v>-2.180564211739937</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.005393744332692478</v>
       </c>
       <c r="E28">
-        <v>-22.92717690234979</v>
+        <v>-23.51710573980302</v>
       </c>
       <c r="F28">
-        <v>0.9577706693803226</v>
+        <v>2.283400397141149</v>
       </c>
       <c r="G28">
-        <v>-4.539286735854568</v>
+        <v>-3.065673727400149</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.01519897288961385</v>
       </c>
       <c r="E29">
-        <v>-21.42945657989695</v>
+        <v>-22.00335914783702</v>
       </c>
       <c r="F29">
-        <v>0.8555799531013644</v>
+        <v>1.964681068709623</v>
       </c>
       <c r="G29">
-        <v>-4.176419724817136</v>
+        <v>-3.117858275081558</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.0476383996771218</v>
       </c>
       <c r="E30">
-        <v>-21.9777823266417</v>
+        <v>-23.11327454169501</v>
       </c>
       <c r="F30">
-        <v>1.213318699674359</v>
+        <v>2.13192182039562</v>
       </c>
       <c r="G30">
-        <v>-3.748066093896307</v>
+        <v>-1.894812469792575</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1006357797422836</v>
       </c>
       <c r="E31">
-        <v>-21.38836520675135</v>
+        <v>-21.94380518616215</v>
       </c>
       <c r="F31">
-        <v>0.9546858291722973</v>
+        <v>1.809039117397623</v>
       </c>
       <c r="G31">
-        <v>-3.479553890022268</v>
+        <v>-2.653483393881144</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.1706635757931247</v>
       </c>
       <c r="E32">
-        <v>-21.41664552692924</v>
+        <v>-22.19967302454354</v>
       </c>
       <c r="F32">
-        <v>0.9803801292723323</v>
+        <v>1.400165251049815</v>
       </c>
       <c r="G32">
-        <v>-3.827533998844499</v>
+        <v>-5.562338805873836</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2526364942250401</v>
       </c>
       <c r="E33">
-        <v>-20.67558792641804</v>
+        <v>-21.19633979493009</v>
       </c>
       <c r="F33">
-        <v>0.7103721175950278</v>
+        <v>1.665065549321458</v>
       </c>
       <c r="G33">
-        <v>-3.068879480863727</v>
+        <v>-1.387168119887764</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.3427953433888693</v>
       </c>
       <c r="E34">
-        <v>-20.65873294616149</v>
+        <v>-20.22461078541617</v>
       </c>
       <c r="F34">
-        <v>0.4435549771533071</v>
+        <v>1.84409893935371</v>
       </c>
       <c r="G34">
-        <v>-3.922942078128473</v>
+        <v>-3.835474555018355</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4364609019934262</v>
       </c>
       <c r="E35">
-        <v>-19.8784859315879</v>
+        <v>-20.73030547785272</v>
       </c>
       <c r="F35">
-        <v>0.5351666133311128</v>
+        <v>2.03460687464954</v>
       </c>
       <c r="G35">
-        <v>-3.896062311113501</v>
+        <v>-3.774414303018648</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5326362651643336</v>
       </c>
       <c r="E36">
-        <v>-19.86264532950907</v>
+        <v>-18.34729112927035</v>
       </c>
       <c r="F36">
-        <v>0.9533123960184557</v>
+        <v>2.114933661699008</v>
       </c>
       <c r="G36">
-        <v>-3.990551648360831</v>
+        <v>-2.105952514699724</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6305576432736466</v>
       </c>
       <c r="E37">
-        <v>-19.59217316245294</v>
+        <v>-20.03006754204665</v>
       </c>
       <c r="F37">
-        <v>0.6421751144247529</v>
+        <v>1.795274964632707</v>
       </c>
       <c r="G37">
-        <v>-3.775710385534629</v>
+        <v>-4.099537422457787</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.731961060059565</v>
       </c>
       <c r="E38">
-        <v>-19.97661796333412</v>
+        <v>-19.50556156858224</v>
       </c>
       <c r="F38">
-        <v>0.4471633455599018</v>
+        <v>1.846837521987365</v>
       </c>
       <c r="G38">
-        <v>-3.837942033631057</v>
+        <v>-2.096144943458543</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8361461630396941</v>
       </c>
       <c r="E39">
-        <v>-18.39605373738495</v>
+        <v>-19.82943350113682</v>
       </c>
       <c r="F39">
-        <v>0.8623974168264044</v>
+        <v>2.276801622410448</v>
       </c>
       <c r="G39">
-        <v>-3.431539774942913</v>
+        <v>-2.38316979937097</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9417529846349296</v>
       </c>
       <c r="E40">
-        <v>-17.62791586230787</v>
+        <v>-20.32126200616188</v>
       </c>
       <c r="F40">
-        <v>0.7353623054026833</v>
+        <v>1.853224234662949</v>
       </c>
       <c r="G40">
-        <v>-3.958828798324119</v>
+        <v>-1.842739483644187</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.04438254401791</v>
       </c>
       <c r="E41">
-        <v>-17.46844565012776</v>
+        <v>-17.46576479351522</v>
       </c>
       <c r="F41">
-        <v>0.4183295330032566</v>
+        <v>1.85290779831508</v>
       </c>
       <c r="G41">
-        <v>-3.061191578749948</v>
+        <v>-2.231114711084742</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.138440361438585</v>
       </c>
       <c r="E42">
-        <v>-17.09314383826807</v>
+        <v>-16.67662838446457</v>
       </c>
       <c r="F42">
-        <v>0.2941257813623043</v>
+        <v>0.8328197303420452</v>
       </c>
       <c r="G42">
-        <v>-4.340211742621498</v>
+        <v>-2.280323190811735</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.216448561167441</v>
       </c>
       <c r="E43">
-        <v>-17.3154420988306</v>
+        <v>-16.90829605774898</v>
       </c>
       <c r="F43">
-        <v>0.6923982016890842</v>
+        <v>1.35751592694928</v>
       </c>
       <c r="G43">
-        <v>-4.249167688011585</v>
+        <v>-3.513212660779051</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.271095904274337</v>
       </c>
       <c r="E44">
-        <v>-17.4568980414082</v>
+        <v>-17.55718109830806</v>
       </c>
       <c r="F44">
-        <v>0.04093694143144101</v>
+        <v>1.151855495121441</v>
       </c>
       <c r="G44">
-        <v>-3.939420372800004</v>
+        <v>-2.528373697041077</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.295562755151756</v>
       </c>
       <c r="E45">
-        <v>-15.7440118049549</v>
+        <v>-16.88352983340103</v>
       </c>
       <c r="F45">
-        <v>0.7118118201410935</v>
+        <v>1.35902189888757</v>
       </c>
       <c r="G45">
-        <v>-3.788503868394903</v>
+        <v>-1.841932303140564</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.28583922910869</v>
       </c>
       <c r="E46">
-        <v>-15.58530690488209</v>
+        <v>-13.87502001250919</v>
       </c>
       <c r="F46">
-        <v>0.5419120090921092</v>
+        <v>1.193664854675538</v>
       </c>
       <c r="G46">
-        <v>-4.85534712134652</v>
+        <v>-1.811498973176714</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.240874299734641</v>
       </c>
       <c r="E47">
-        <v>-15.21415317521343</v>
+        <v>-16.49316631699183</v>
       </c>
       <c r="F47">
-        <v>0.3578529140270731</v>
+        <v>1.217548343633053</v>
       </c>
       <c r="G47">
-        <v>-4.247110362093813</v>
+        <v>-3.047633571266322</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.163720920034147</v>
       </c>
       <c r="E48">
-        <v>-15.35121649800358</v>
+        <v>-14.4045390067001</v>
       </c>
       <c r="F48">
-        <v>0.3135708777756199</v>
+        <v>1.679956281754182</v>
       </c>
       <c r="G48">
-        <v>-4.119979432773127</v>
+        <v>-2.356880652236699</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.060119069700853</v>
       </c>
       <c r="E49">
-        <v>-13.82172893038693</v>
+        <v>-15.1943003451638</v>
       </c>
       <c r="F49">
-        <v>-0.06604173843569834</v>
+        <v>0.738995524831362</v>
       </c>
       <c r="G49">
-        <v>-3.992523662518057</v>
+        <v>-2.597085757717409</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9393795440603063</v>
       </c>
       <c r="E50">
-        <v>-13.68444371237039</v>
+        <v>-14.08274111524103</v>
       </c>
       <c r="F50">
-        <v>0.03521623614770763</v>
+        <v>0.7447079464410674</v>
       </c>
       <c r="G50">
-        <v>-4.494471811795672</v>
+        <v>-3.173609510598083</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8126558367830534</v>
       </c>
       <c r="E51">
-        <v>-12.63000665358038</v>
+        <v>-12.94350385218338</v>
       </c>
       <c r="F51">
-        <v>0.1665721119444308</v>
+        <v>0.6360675615639122</v>
       </c>
       <c r="G51">
-        <v>-4.41636561379465</v>
+        <v>-3.099962492696346</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.6925309782853714</v>
       </c>
       <c r="E52">
-        <v>-12.62800053959498</v>
+        <v>-12.54123497760802</v>
       </c>
       <c r="F52">
-        <v>-0.02260877877211466</v>
+        <v>0.8970911003904533</v>
       </c>
       <c r="G52">
-        <v>-5.101904671766316</v>
+        <v>-2.878040353744862</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.5922410444163382</v>
       </c>
       <c r="E53">
-        <v>-11.70675495831857</v>
+        <v>-13.57165753873536</v>
       </c>
       <c r="F53">
-        <v>-0.1313427691657862</v>
+        <v>1.402658636932242</v>
       </c>
       <c r="G53">
-        <v>-5.464003876958837</v>
+        <v>-2.519803146327807</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.5234334471823946</v>
       </c>
       <c r="E54">
-        <v>-11.75319898774124</v>
+        <v>-12.93692397945024</v>
       </c>
       <c r="F54">
-        <v>-0.1545726762424927</v>
+        <v>0.6200502494633809</v>
       </c>
       <c r="G54">
-        <v>-4.225490393238632</v>
+        <v>-2.922284345252415</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.4956267303554057</v>
       </c>
       <c r="E55">
-        <v>-11.60340159604151</v>
+        <v>-10.65624408649321</v>
       </c>
       <c r="F55">
-        <v>0.09908336290354951</v>
+        <v>0.8971987881528172</v>
       </c>
       <c r="G55">
-        <v>-4.791419081703859</v>
+        <v>-3.180549294196308</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.5139434188998941</v>
       </c>
       <c r="E56">
-        <v>-11.04686572592085</v>
+        <v>-11.74223555216867</v>
       </c>
       <c r="F56">
-        <v>-0.2403385236587423</v>
+        <v>0.8312739967684213</v>
       </c>
       <c r="G56">
-        <v>-5.355493879988001</v>
+        <v>-5.286998379934592</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.5806700636524662</v>
       </c>
       <c r="E57">
-        <v>-10.54482098353448</v>
+        <v>-12.82351287640214</v>
       </c>
       <c r="F57">
-        <v>-0.3550069381260695</v>
+        <v>1.102902295085602</v>
       </c>
       <c r="G57">
-        <v>-5.441438916294536</v>
+        <v>-2.76028387441951</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6922503149385444</v>
       </c>
       <c r="E58">
-        <v>-11.36988177688798</v>
+        <v>-10.0079341621331</v>
       </c>
       <c r="F58">
-        <v>-0.2236676296774023</v>
+        <v>0.5324793894764313</v>
       </c>
       <c r="G58">
-        <v>-6.234451105224253</v>
+        <v>-4.348464014843501</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8424507831461832</v>
       </c>
       <c r="E59">
-        <v>-10.25699570408096</v>
+        <v>-10.78045107157559</v>
       </c>
       <c r="F59">
-        <v>-0.2935892937803057</v>
+        <v>0.6249268483636616</v>
       </c>
       <c r="G59">
-        <v>-5.458530799397684</v>
+        <v>-3.159559319880541</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.019484632142885</v>
       </c>
       <c r="E60">
-        <v>-10.12800665044648</v>
+        <v>-11.12032210279927</v>
       </c>
       <c r="F60">
-        <v>-0.8110057976517385</v>
+        <v>0.08600344161334532</v>
       </c>
       <c r="G60">
-        <v>-5.440992670162451</v>
+        <v>-3.427471060209202</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.21106022403363</v>
       </c>
       <c r="E61">
-        <v>-9.678990338689932</v>
+        <v>-10.16115508018263</v>
       </c>
       <c r="F61">
-        <v>-0.4608805758778743</v>
+        <v>0.2657649665926576</v>
       </c>
       <c r="G61">
-        <v>-5.597546313206678</v>
+        <v>-2.83078091962418</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.403011065069325</v>
       </c>
       <c r="E62">
-        <v>-9.50731588905915</v>
+        <v>-9.500070330646876</v>
       </c>
       <c r="F62">
-        <v>-0.834272981261571</v>
+        <v>1.178046815663156</v>
       </c>
       <c r="G62">
-        <v>-5.486926490773118</v>
+        <v>-3.983519990558941</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.583993121353238</v>
       </c>
       <c r="E63">
-        <v>-8.712410204122733</v>
+        <v>-9.448164961570958</v>
       </c>
       <c r="F63">
-        <v>-0.4624304512885122</v>
+        <v>0.05941284798348119</v>
       </c>
       <c r="G63">
-        <v>-5.511095968779988</v>
+        <v>-3.33701106303687</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.743864424846461</v>
       </c>
       <c r="E64">
-        <v>-9.1144435980497</v>
+        <v>-10.48232804222863</v>
       </c>
       <c r="F64">
-        <v>-1.348449740220655</v>
+        <v>0.3577576517757511</v>
       </c>
       <c r="G64">
-        <v>-5.850351309475656</v>
+        <v>-3.411297919142699</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.876992457196828</v>
       </c>
       <c r="E65">
-        <v>-8.696239023441342</v>
+        <v>-9.360887682021128</v>
       </c>
       <c r="F65">
-        <v>-0.895371704157257</v>
+        <v>-0.3589160038998803</v>
       </c>
       <c r="G65">
-        <v>-5.448381981114321</v>
+        <v>-4.72210327626059</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.980459142546891</v>
       </c>
       <c r="E66">
-        <v>-9.056547057861634</v>
+        <v>-8.45380716744071</v>
       </c>
       <c r="F66">
-        <v>-1.116498583762765</v>
+        <v>-0.3503192069936271</v>
       </c>
       <c r="G66">
-        <v>-6.468277515993403</v>
+        <v>-4.978999955814195</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.054006587911825</v>
       </c>
       <c r="E67">
-        <v>-8.688341364771965</v>
+        <v>-8.830739229943159</v>
       </c>
       <c r="F67">
-        <v>-1.206885892919233</v>
+        <v>-0.2240122305169669</v>
       </c>
       <c r="G67">
-        <v>-5.269985246148871</v>
+        <v>-3.029508103371949</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.09716753243915</v>
       </c>
       <c r="E68">
-        <v>-8.901908727447706</v>
+        <v>-8.211108131473624</v>
       </c>
       <c r="F68">
-        <v>-1.306205487780089</v>
+        <v>-0.1981381746905243</v>
       </c>
       <c r="G68">
-        <v>-5.967428575938202</v>
+        <v>-4.978458554256886</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.108779060380471</v>
       </c>
       <c r="E69">
-        <v>-9.396848294116039</v>
+        <v>-9.483364790032581</v>
       </c>
       <c r="F69">
-        <v>-1.229572390979704</v>
+        <v>-0.6543747756607968</v>
       </c>
       <c r="G69">
-        <v>-5.898411361656842</v>
+        <v>-4.405678675175539</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.087504028742711</v>
       </c>
       <c r="E70">
-        <v>-9.601793442281176</v>
+        <v>-9.778639409228719</v>
       </c>
       <c r="F70">
-        <v>-1.31824000940796</v>
+        <v>-0.6497922471885099</v>
       </c>
       <c r="G70">
-        <v>-5.37381293995438</v>
+        <v>-3.389477795772391</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.033832167392864</v>
       </c>
       <c r="E71">
-        <v>-8.703634021495867</v>
+        <v>-9.46062279356606</v>
       </c>
       <c r="F71">
-        <v>-1.569472245533411</v>
+        <v>-0.6665236119902543</v>
       </c>
       <c r="G71">
-        <v>-5.4151793001543</v>
+        <v>-5.612643213601682</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.949381459987491</v>
       </c>
       <c r="E72">
-        <v>-9.504041802351603</v>
+        <v>-9.958130004996741</v>
       </c>
       <c r="F72">
-        <v>-1.325888325638008</v>
+        <v>-0.7698616171220899</v>
       </c>
       <c r="G72">
-        <v>-5.279139854299722</v>
+        <v>-4.740829207700341</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.838557225707446</v>
       </c>
       <c r="E73">
-        <v>-9.6490978817653</v>
+        <v>-9.679470356934745</v>
       </c>
       <c r="F73">
-        <v>-1.882964575653272</v>
+        <v>-0.5162213169567008</v>
       </c>
       <c r="G73">
-        <v>-4.870460427849324</v>
+        <v>-4.094638558669536</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.706287112700835</v>
       </c>
       <c r="E74">
-        <v>-10.8892657735059</v>
+        <v>-10.30133399309006</v>
       </c>
       <c r="F74">
-        <v>-2.100907210962419</v>
+        <v>-0.8394005754849</v>
       </c>
       <c r="G74">
-        <v>-4.582106677205322</v>
+        <v>-3.667229919557827</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.559865422933287</v>
       </c>
       <c r="E75">
-        <v>-10.29973091329135</v>
+        <v>-10.08222377822893</v>
       </c>
       <c r="F75">
-        <v>-1.996957870687318</v>
+        <v>-0.7313035996239813</v>
       </c>
       <c r="G75">
-        <v>-5.029865452428707</v>
+        <v>-2.93649531582637</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.406189678746337</v>
       </c>
       <c r="E76">
-        <v>-11.25770241876996</v>
+        <v>-10.80732303633711</v>
       </c>
       <c r="F76">
-        <v>-1.803297997423835</v>
+        <v>-0.6728523389476426</v>
       </c>
       <c r="G76">
-        <v>-4.071604383322234</v>
+        <v>-3.616367704164874</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.253222334763734</v>
       </c>
       <c r="E77">
-        <v>-10.46561797314033</v>
+        <v>-11.49489030186971</v>
       </c>
       <c r="F77">
-        <v>-2.343680987537885</v>
+        <v>-1.266031325479118</v>
       </c>
       <c r="G77">
-        <v>-4.869515436040203</v>
+        <v>-3.520723376928621</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.108045739775009</v>
       </c>
       <c r="E78">
-        <v>-11.41332342804356</v>
+        <v>-11.39372872101237</v>
       </c>
       <c r="F78">
-        <v>-1.872561109441513</v>
+        <v>-1.142072770589394</v>
       </c>
       <c r="G78">
-        <v>-4.078941194729152</v>
+        <v>-3.106534779479914</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.9772762644100773</v>
       </c>
       <c r="E79">
-        <v>-11.67408654682724</v>
+        <v>-13.32524968255599</v>
       </c>
       <c r="F79">
-        <v>-2.088847009945062</v>
+        <v>-1.099865794681954</v>
       </c>
       <c r="G79">
-        <v>-3.634742544897765</v>
+        <v>-4.342242818766794</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.8672985164268532</v>
       </c>
       <c r="E80">
-        <v>-11.66694514331714</v>
+        <v>-11.49292947262439</v>
       </c>
       <c r="F80">
-        <v>-2.345490141945599</v>
+        <v>-1.075344462824283</v>
       </c>
       <c r="G80">
-        <v>-4.04036715407632</v>
+        <v>-2.891453987479872</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.7826382657663298</v>
       </c>
       <c r="E81">
-        <v>-12.93335101345819</v>
+        <v>-11.11456188386151</v>
       </c>
       <c r="F81">
-        <v>-2.054956842761728</v>
+        <v>-1.60498269935662</v>
       </c>
       <c r="G81">
-        <v>-3.083471073138577</v>
+        <v>-2.486659527355856</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.7283427840040231</v>
       </c>
       <c r="E82">
-        <v>-15.12814839685975</v>
+        <v>-13.35741543343247</v>
       </c>
       <c r="F82">
-        <v>-2.164116614000438</v>
+        <v>-1.629663906123031</v>
       </c>
       <c r="G82">
-        <v>-3.843700577467883</v>
+        <v>-2.778891681883121</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.7074794135393118</v>
       </c>
       <c r="E83">
-        <v>-14.57820598489425</v>
+        <v>-13.87519209452149</v>
       </c>
       <c r="F83">
-        <v>-2.472921212987858</v>
+        <v>-1.670554606227423</v>
       </c>
       <c r="G83">
-        <v>-2.907607441217019</v>
+        <v>-3.187118299758317</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.7243887549748097</v>
       </c>
       <c r="E84">
-        <v>-16.14758035157047</v>
+        <v>-15.4943932607041</v>
       </c>
       <c r="F84">
-        <v>-2.767251748346161</v>
+        <v>-0.9430011730834229</v>
       </c>
       <c r="G84">
-        <v>-4.094930587388327</v>
+        <v>-1.706795193214833</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.7811885865203346</v>
       </c>
       <c r="E85">
-        <v>-16.26309719503213</v>
+        <v>-16.50723628573366</v>
       </c>
       <c r="F85">
-        <v>-2.477395225330378</v>
+        <v>-1.476350495580302</v>
       </c>
       <c r="G85">
-        <v>-3.050150268202416</v>
+        <v>-2.622003354239832</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8804079841492219</v>
       </c>
       <c r="E86">
-        <v>-17.1725687438886</v>
+        <v>-17.66109599136207</v>
       </c>
       <c r="F86">
-        <v>-3.044100418035784</v>
+        <v>-1.936206233733405</v>
       </c>
       <c r="G86">
-        <v>-3.15702293561509</v>
+        <v>-2.011053024757463</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.021330413872345</v>
       </c>
       <c r="E87">
-        <v>-18.3802629485202</v>
+        <v>-18.29551255746665</v>
       </c>
       <c r="F87">
-        <v>-2.893349147869913</v>
+        <v>-1.858511998290034</v>
       </c>
       <c r="G87">
-        <v>-2.927380082334233</v>
+        <v>-3.215950393601157</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.201708834051707</v>
       </c>
       <c r="E88">
-        <v>-20.54154509579099</v>
+        <v>-20.29536819178602</v>
       </c>
       <c r="F88">
-        <v>-3.040288271248101</v>
+        <v>-1.83556704959989</v>
       </c>
       <c r="G88">
-        <v>-3.109373036128833</v>
+        <v>-2.754955170606972</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.41759691397642</v>
       </c>
       <c r="E89">
-        <v>-21.54425792446539</v>
+        <v>-24.75464258814517</v>
       </c>
       <c r="F89">
-        <v>-3.260596723859643</v>
+        <v>-2.050755363294729</v>
       </c>
       <c r="G89">
-        <v>-3.466862125030335</v>
+        <v>-3.068892605749964</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.663546445420139</v>
       </c>
       <c r="E90">
-        <v>-23.39576527876749</v>
+        <v>-24.11919352996684</v>
       </c>
       <c r="F90">
-        <v>-3.14534348200594</v>
+        <v>-1.599195724680663</v>
       </c>
       <c r="G90">
-        <v>-3.155510292476186</v>
+        <v>-2.336448485586037</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.93555423877526</v>
       </c>
       <c r="E91">
-        <v>-24.66773211498996</v>
+        <v>-24.46363379146425</v>
       </c>
       <c r="F91">
-        <v>-3.213943071733975</v>
+        <v>-2.273206802377314</v>
       </c>
       <c r="G91">
-        <v>-2.876212713336252</v>
+        <v>-0.7956032473785951</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.225798480028172</v>
       </c>
       <c r="E92">
-        <v>-27.06609799045832</v>
+        <v>-27.2274973325657</v>
       </c>
       <c r="F92">
-        <v>-3.631842829302687</v>
+        <v>-2.000284594176961</v>
       </c>
       <c r="G92">
-        <v>-3.447939320297018</v>
+        <v>-3.236110218862386</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.531087877813643</v>
       </c>
       <c r="E93">
-        <v>-28.53523005650075</v>
+        <v>-28.50240314841914</v>
       </c>
       <c r="F93">
-        <v>-3.449788383352425</v>
+        <v>-2.714869107262732</v>
       </c>
       <c r="G93">
-        <v>-3.611521339921575</v>
+        <v>-3.50388742910711</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.842659067638373</v>
       </c>
       <c r="E94">
-        <v>-29.81523493408683</v>
+        <v>-31.14375788219109</v>
       </c>
       <c r="F94">
-        <v>-3.734017806600991</v>
+        <v>-2.501577754920304</v>
       </c>
       <c r="G94">
-        <v>-3.68576554014713</v>
+        <v>-2.331027907569834</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.158829588903781</v>
       </c>
       <c r="E95">
-        <v>-32.96331232389506</v>
+        <v>-33.96505605913182</v>
       </c>
       <c r="F95">
-        <v>-3.366192030164108</v>
+        <v>-2.81254439282903</v>
       </c>
       <c r="G95">
-        <v>-4.027793513060528</v>
+        <v>-3.820692651893056</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.473287497860181</v>
       </c>
       <c r="E96">
-        <v>-34.30560409721964</v>
+        <v>-34.90666618802073</v>
       </c>
       <c r="F96">
-        <v>-3.707905180962543</v>
+        <v>-2.895325632492993</v>
       </c>
       <c r="G96">
-        <v>-3.167060192365431</v>
+        <v>-3.479809825303904</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.783702192959464</v>
       </c>
       <c r="E97">
-        <v>-37.56495288610735</v>
+        <v>-38.35569690343072</v>
       </c>
       <c r="F97">
-        <v>-3.682974635607889</v>
+        <v>-3.197062600799727</v>
       </c>
       <c r="G97">
-        <v>-3.956840378059096</v>
+        <v>-2.573579086465547</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.08522061861866</v>
       </c>
       <c r="E98">
-        <v>-39.74234507966043</v>
+        <v>-40.34343660554256</v>
       </c>
       <c r="F98">
-        <v>-3.968328153422054</v>
+        <v>-3.310479352121424</v>
       </c>
       <c r="G98">
-        <v>-4.124907827555414</v>
+        <v>-2.119569584171419</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.36843022815562</v>
       </c>
       <c r="E99">
-        <v>-41.8430385089456</v>
+        <v>-43.92649430192057</v>
       </c>
       <c r="F99">
-        <v>-4.125307089722171</v>
+        <v>-3.205888855476556</v>
       </c>
       <c r="G99">
-        <v>-4.276490419937081</v>
+        <v>-2.827630946927113</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.62893438377481</v>
       </c>
       <c r="E100">
-        <v>-45.06773767896361</v>
+        <v>-45.69336674125631</v>
       </c>
       <c r="F100">
-        <v>-4.219896706713041</v>
+        <v>-3.050896344208351</v>
       </c>
       <c r="G100">
-        <v>-4.305174858809747</v>
+        <v>-3.582000189551251</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.846099935562286</v>
       </c>
       <c r="E101">
-        <v>-46.7150267051788</v>
+        <v>-46.900526585955</v>
       </c>
       <c r="F101">
-        <v>-4.59927572331677</v>
+        <v>-4.024868370500134</v>
       </c>
       <c r="G101">
-        <v>-4.42954628079894</v>
+        <v>-4.64906328434735</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.027486995760917</v>
       </c>
       <c r="E102">
-        <v>-50.04076858361147</v>
+        <v>-48.95652284466596</v>
       </c>
       <c r="F102">
-        <v>-4.618898090354285</v>
+        <v>-3.59656100488265</v>
       </c>
       <c r="G102">
-        <v>-5.287310095982739</v>
+        <v>-3.469933348409976</v>
       </c>
     </row>
   </sheetData>
